--- a/data/trans_bre/IQ2601_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IQ2601_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,66</t>
+          <t>9,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 15,63</t>
+          <t>-13,93; 14,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 12,09</t>
+          <t>-17,28; 13,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 16,7</t>
+          <t>-12,21; 18,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 35,68</t>
+          <t>-19,78; 34,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 29,85</t>
+          <t>-21,09; 27,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 33,25</t>
+          <t>-33,88; 38,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 32,77</t>
+          <t>-18,44; 38,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 73,55</t>
+          <t>-26,1; 70,06</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 0,98</t>
+          <t>-12,14; 1,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 19,3</t>
+          <t>-5,65; 16,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 10,25</t>
+          <t>-11,35; 10,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 31,05</t>
+          <t>-21,48; 29,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 0,95</t>
+          <t>-12,72; 1,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 49,84</t>
+          <t>-10,59; 43,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 17,88</t>
+          <t>-17,18; 19,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,42; 61,07</t>
+          <t>-27,91; 58,96</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,57%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 27,38</t>
+          <t>-1,08; 25,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 21,3</t>
+          <t>-5,58; 20,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 10,48</t>
+          <t>-17,33; 9,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 25,92</t>
+          <t>-26,87; 23,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 89,19</t>
+          <t>-2,28; 85,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 76,83</t>
+          <t>-14,2; 76,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 16,03</t>
+          <t>-23,38; 15,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,94; 55,38</t>
+          <t>-36,75; 52,17</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-37,13</t>
+          <t>-36,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-37,13%</t>
+          <t>-36,55%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 24,72</t>
+          <t>0,08; 24,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 19,53</t>
+          <t>-5,71; 19,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 8,6</t>
+          <t>-16,85; 8,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,19; -15,9</t>
+          <t>-62,78; -15,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 48,27</t>
+          <t>0,27; 47,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 35,6</t>
+          <t>-8,79; 35,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 14,27</t>
+          <t>-23,71; 14,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,19; -15,9</t>
+          <t>-62,78; -15,39</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-25,53</t>
+          <t>-25,25</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-25,53%</t>
+          <t>-25,25%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 29,33</t>
+          <t>-4,36; 28,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 20,0</t>
+          <t>-13,89; 19,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 26,28</t>
+          <t>-1,79; 25,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-47,1; -8,55</t>
+          <t>-46,31; -10,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 61,98</t>
+          <t>-6,51; 58,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 39,72</t>
+          <t>-20,64; 36,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 39,65</t>
+          <t>-1,37; 38,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-47,1; -8,55</t>
+          <t>-46,31; -10,53</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-1,66%</t>
+          <t>-1,47%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 7,96</t>
+          <t>-20,23; 8,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 21,65</t>
+          <t>-8,77; 22,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 11,41</t>
+          <t>-19,65; 11,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 28,6</t>
+          <t>-35,83; 26,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,38; 18,57</t>
+          <t>-37,66; 22,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 80,32</t>
+          <t>-22,94; 82,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 24,88</t>
+          <t>-33,39; 26,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,23; 59,07</t>
+          <t>-52,17; 55,61</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>-4,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>-6,1%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 9,35</t>
+          <t>-10,02; 9,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 11,62</t>
+          <t>-8,15; 12,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 7,48</t>
+          <t>-10,36; 8,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 19,72</t>
+          <t>-24,01; 15,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 16,57</t>
+          <t>-15,21; 17,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 28,19</t>
+          <t>-16,82; 31,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 12,6</t>
+          <t>-15,02; 14,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 34,55</t>
+          <t>-31,5; 25,13</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-7,88</t>
+          <t>-7,58</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-9,35%</t>
+          <t>-9,0%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 9,85</t>
+          <t>-4,55; 10,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 10,04</t>
+          <t>-6,78; 10,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 8,7</t>
+          <t>-7,71; 9,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 8,72</t>
+          <t>-26,14; 9,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 13,79</t>
+          <t>-5,66; 14,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 18,6</t>
+          <t>-10,93; 19,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 14,42</t>
+          <t>-11,37; 15,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 11,11</t>
+          <t>-29,37; 11,2</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,45</t>
+          <t>-5,31</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-4,72%</t>
+          <t>-7,24%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 6,88</t>
+          <t>-1,39; 6,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 7,87</t>
+          <t>-0,62; 7,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,77</t>
+          <t>-4,12; 4,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 4,71</t>
+          <t>-14,2; 3,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 10,87</t>
+          <t>-2,11; 10,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 17,02</t>
+          <t>-1,2; 16,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,97</t>
+          <t>-6,23; 6,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 6,9</t>
+          <t>-18,36; 5,75</t>
         </is>
       </c>
     </row>
